--- a/output/Data and Chart Outputs/india_coal_stocks.xlsx
+++ b/output/Data and Chart Outputs/india_coal_stocks.xlsx
@@ -28673,7 +28673,7 @@
         <v>225187.5</v>
       </c>
       <c r="G819" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="820">
@@ -28696,7 +28696,7 @@
         <v>225187.5</v>
       </c>
       <c r="G820" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/india_coal_stocks.xlsx
+++ b/output/Data and Chart Outputs/india_coal_stocks.xlsx
@@ -862,7 +862,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thousand tonnes ('000 t), all-India thermal power plants in CEA's daily coal stock report: Actual_stock_kt (indigenous + imported coal at the plants), Normative_stock_kt (stock the plants should hold), Receipt_kt and Consumption_kt (of the day), Capacity_MW (plants covered). Days_of_stock = actual stock / 7-day average consumption.</t>
+          <t>Thousand tonnes ('000 t), all-India thermal power plants in CEA's daily coal stock report: Actual_stock_kt (indigenous + imported coal at the plants), Normative_stock_kt (stock the plants should hold), Receipt_kt and Consumption_kt (of the day), Capacity_MW (plants covered). Days_of_stock = actual stock / 7-day average consumption (a day more than 1.6x the 15-day median, i.e. reported twice, left out of the average).</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2024-06-05 to 2026-10-02 (the NPP archive of this report starts in 2022). Totals from: grand total row.</t>
+          <t>Daily from 2024-06-05 to 2026-10-02 (pulled from 2024-06-05, where the NPP archive of this report starts). Totals from: grand total row.</t>
         </is>
       </c>
     </row>
@@ -30267,7 +30267,7 @@
         <v>216786</v>
       </c>
       <c r="G482" t="n">
-        <v>26.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="483">
@@ -30290,7 +30290,7 @@
         <v>216786</v>
       </c>
       <c r="G483" t="n">
-        <v>16.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="484">
@@ -30313,7 +30313,7 @@
         <v>216786</v>
       </c>
       <c r="G484" t="n">
-        <v>16.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="485">
@@ -30336,7 +30336,7 @@
         <v>216786</v>
       </c>
       <c r="G485" t="n">
-        <v>16.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="486">
@@ -30359,7 +30359,7 @@
         <v>216786</v>
       </c>
       <c r="G486" t="n">
-        <v>16.8</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="487">
@@ -30382,7 +30382,7 @@
         <v>216786</v>
       </c>
       <c r="G487" t="n">
-        <v>16.9</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="488">
@@ -30405,7 +30405,7 @@
         <v>216786</v>
       </c>
       <c r="G488" t="n">
-        <v>16.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="489">

--- a/output/Data and Chart Outputs/india_coal_stocks.xlsx
+++ b/output/Data and Chart Outputs/india_coal_stocks.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$821</f>
+              <f>'Chart'!$D$2:$D$825</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$821</f>
+              <f>'Chart'!$B$2:$B$825</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$821</f>
+              <f>'Chart'!$D$2:$D$825</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$821</f>
+              <f>'Chart'!$C$2:$C$825</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal stock'!$D$2:$D$821</f>
+              <f>'Chart - Coal stock'!$D$2:$D$825</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal stock'!$B$2:$B$821</f>
+              <f>'Chart - Coal stock'!$B$2:$B$825</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -404,12 +404,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal stock'!$D$2:$D$821</f>
+              <f>'Chart - Coal stock'!$D$2:$D$825</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal stock'!$C$2:$C$821</f>
+              <f>'Chart - Coal stock'!$C$2:$C$825</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -877,7 +877,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2024-06-05 to 2026-10-02 (pulled from 2024-06-05, where the NPP archive of this report starts). Totals from: grand total row.</t>
+          <t>Daily from 2024-06-05 to 2026-10-06 (pulled from 2024-06-05, where the NPP archive of this report starts). Totals from: grand total row.</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10023,6 +10023,50 @@
       </c>
       <c r="C821" t="n">
         <v>23.7</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B822" t="n">
+        <v>8</v>
+      </c>
+      <c r="C822" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B823" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C823" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B824" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C824" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B825" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C825" t="n">
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>
@@ -10037,7 +10081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19153,6 +19197,50 @@
       </c>
       <c r="C821" t="n">
         <v>60.9835</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B822" t="n">
+        <v>20.8923</v>
+      </c>
+      <c r="C822" t="n">
+        <v>60.9835</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B823" t="n">
+        <v>20.725</v>
+      </c>
+      <c r="C823" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B824" t="n">
+        <v>20.5878</v>
+      </c>
+      <c r="C824" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B825" t="n">
+        <v>20.4362</v>
+      </c>
+      <c r="C825" t="n">
+        <v>61.1729</v>
       </c>
     </row>
   </sheetData>
@@ -19167,7 +19255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G821"/>
+  <dimension ref="A1:G825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38067,6 +38155,98 @@
         <v>8.199999999999999</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B822" t="n">
+        <v>20892.3</v>
+      </c>
+      <c r="C822" t="n">
+        <v>60983.5</v>
+      </c>
+      <c r="D822" t="n">
+        <v>2538.1</v>
+      </c>
+      <c r="E822" t="n">
+        <v>2691.3</v>
+      </c>
+      <c r="F822" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G822" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B823" t="n">
+        <v>20725</v>
+      </c>
+      <c r="C823" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D823" t="n">
+        <v>2524.8</v>
+      </c>
+      <c r="E823" t="n">
+        <v>2686.3</v>
+      </c>
+      <c r="F823" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G823" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B824" t="n">
+        <v>20587.8</v>
+      </c>
+      <c r="C824" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D824" t="n">
+        <v>2608.8</v>
+      </c>
+      <c r="E824" t="n">
+        <v>2742.2</v>
+      </c>
+      <c r="F824" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G824" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B825" t="n">
+        <v>20436.2</v>
+      </c>
+      <c r="C825" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D825" t="n">
+        <v>2614.4</v>
+      </c>
+      <c r="E825" t="n">
+        <v>2770.8</v>
+      </c>
+      <c r="F825" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G825" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/india_coal_stocks.xlsx
+++ b/output/Data and Chart Outputs/india_coal_stocks.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India: days of coal at power plants (CEA daily coal stock report) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -192,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$825</f>
+              <f>'Chart'!$D$2:$D$845</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$825</f>
+              <f>'Chart'!$B$2:$B$845</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +229,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$825</f>
+              <f>'Chart'!$D$2:$D$845</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$825</f>
+              <f>'Chart'!$C$2:$C$845</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -332,6 +333,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India coal stock at power plants (CEA) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -368,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal stock'!$D$2:$D$825</f>
+              <f>'Chart - Coal stock'!$D$2:$D$845</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal stock'!$B$2:$B$825</f>
+              <f>'Chart - Coal stock'!$B$2:$B$845</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -404,12 +406,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal stock'!$D$2:$D$825</f>
+              <f>'Chart - Coal stock'!$D$2:$D$845</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal stock'!$C$2:$C$825</f>
+              <f>'Chart - Coal stock'!$C$2:$C$845</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -877,7 +879,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Daily from 2024-06-05 to 2026-10-06 (pulled from 2024-06-05, where the NPP archive of this report starts). Totals from: grand total row.</t>
+          <t>Daily from 2024-06-05 to 2026-10-26 (pulled from 2024-06-05, where the NPP archive of this report starts). Totals from: grand total row.</t>
         </is>
       </c>
     </row>
@@ -907,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10067,6 +10069,226 @@
       </c>
       <c r="C825" t="n">
         <v>22.6</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B826" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C826" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B827" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C827" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B828" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C828" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B829" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C829" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B830" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C830" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B831" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C831" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B832" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C832" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B833" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C833" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B834" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C834" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B835" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C835" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B836" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C836" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B837" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C837" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B838" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C838" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B839" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C839" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B840" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C840" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B841" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C841" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B842" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C842" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B843" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C843" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B844" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C844" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B845" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C845" t="n">
+        <v>23.4</v>
       </c>
     </row>
   </sheetData>
@@ -10081,7 +10303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19240,6 +19462,226 @@
         <v>20.4362</v>
       </c>
       <c r="C825" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B826" t="n">
+        <v>20.6529</v>
+      </c>
+      <c r="C826" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B827" t="n">
+        <v>20.6189</v>
+      </c>
+      <c r="C827" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B828" t="n">
+        <v>20.6663</v>
+      </c>
+      <c r="C828" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B829" t="n">
+        <v>20.7785</v>
+      </c>
+      <c r="C829" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B830" t="n">
+        <v>20.8663</v>
+      </c>
+      <c r="C830" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B831" t="n">
+        <v>20.7831</v>
+      </c>
+      <c r="C831" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B832" t="n">
+        <v>20.4743</v>
+      </c>
+      <c r="C832" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B833" t="n">
+        <v>20.4489</v>
+      </c>
+      <c r="C833" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B834" t="n">
+        <v>20.4432</v>
+      </c>
+      <c r="C834" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B835" t="n">
+        <v>20.4187</v>
+      </c>
+      <c r="C835" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B836" t="n">
+        <v>20.4562</v>
+      </c>
+      <c r="C836" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B837" t="n">
+        <v>20.4424</v>
+      </c>
+      <c r="C837" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B838" t="n">
+        <v>20.0705</v>
+      </c>
+      <c r="C838" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B839" t="n">
+        <v>20.0904</v>
+      </c>
+      <c r="C839" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B840" t="n">
+        <v>19.7791</v>
+      </c>
+      <c r="C840" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B841" t="n">
+        <v>19.7334</v>
+      </c>
+      <c r="C841" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B842" t="n">
+        <v>19.6858</v>
+      </c>
+      <c r="C842" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B843" t="n">
+        <v>19.689</v>
+      </c>
+      <c r="C843" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B844" t="n">
+        <v>19.9248</v>
+      </c>
+      <c r="C844" t="n">
+        <v>61.1729</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B845" t="n">
+        <v>20.0872</v>
+      </c>
+      <c r="C845" t="n">
         <v>61.1729</v>
       </c>
     </row>
@@ -19255,7 +19697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G825"/>
+  <dimension ref="A1:G845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38247,6 +38689,466 @@
         <v>7.6</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B826" t="n">
+        <v>20652.9</v>
+      </c>
+      <c r="C826" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D826" t="n">
+        <v>2740.5</v>
+      </c>
+      <c r="E826" t="n">
+        <v>2744.7</v>
+      </c>
+      <c r="F826" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G826" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B827" t="n">
+        <v>20618.9</v>
+      </c>
+      <c r="C827" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D827" t="n">
+        <v>2682.1</v>
+      </c>
+      <c r="E827" t="n">
+        <v>2729</v>
+      </c>
+      <c r="F827" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G827" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B828" t="n">
+        <v>20666.3</v>
+      </c>
+      <c r="C828" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D828" t="n">
+        <v>2792.3</v>
+      </c>
+      <c r="E828" t="n">
+        <v>2750.1</v>
+      </c>
+      <c r="F828" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G828" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B829" t="n">
+        <v>20778.5</v>
+      </c>
+      <c r="C829" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D829" t="n">
+        <v>2803.2</v>
+      </c>
+      <c r="E829" t="n">
+        <v>2692.8</v>
+      </c>
+      <c r="F829" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G829" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B830" t="n">
+        <v>20866.3</v>
+      </c>
+      <c r="C830" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D830" t="n">
+        <v>2728.9</v>
+      </c>
+      <c r="E830" t="n">
+        <v>2630.2</v>
+      </c>
+      <c r="F830" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G830" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B831" t="n">
+        <v>20783.1</v>
+      </c>
+      <c r="C831" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D831" t="n">
+        <v>2654.1</v>
+      </c>
+      <c r="E831" t="n">
+        <v>2729.3</v>
+      </c>
+      <c r="F831" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G831" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B832" t="n">
+        <v>20474.3</v>
+      </c>
+      <c r="C832" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D832" t="n">
+        <v>2470.6</v>
+      </c>
+      <c r="E832" t="n">
+        <v>2774.9</v>
+      </c>
+      <c r="F832" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G832" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B833" t="n">
+        <v>20448.9</v>
+      </c>
+      <c r="C833" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2804.2</v>
+      </c>
+      <c r="E833" t="n">
+        <v>2835</v>
+      </c>
+      <c r="F833" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G833" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B834" t="n">
+        <v>20443.2</v>
+      </c>
+      <c r="C834" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>2785.3</v>
+      </c>
+      <c r="E834" t="n">
+        <v>2791.3</v>
+      </c>
+      <c r="F834" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G834" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B835" t="n">
+        <v>20418.7</v>
+      </c>
+      <c r="C835" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D835" t="n">
+        <v>2748.8</v>
+      </c>
+      <c r="E835" t="n">
+        <v>2765.8</v>
+      </c>
+      <c r="F835" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G835" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B836" t="n">
+        <v>20456.2</v>
+      </c>
+      <c r="C836" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D836" t="n">
+        <v>2783.7</v>
+      </c>
+      <c r="E836" t="n">
+        <v>2741</v>
+      </c>
+      <c r="F836" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G836" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B837" t="n">
+        <v>20442.4</v>
+      </c>
+      <c r="C837" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D837" t="n">
+        <v>2653.5</v>
+      </c>
+      <c r="E837" t="n">
+        <v>2669.1</v>
+      </c>
+      <c r="F837" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G837" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B838" t="n">
+        <v>20070.5</v>
+      </c>
+      <c r="C838" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D838" t="n">
+        <v>2307.3</v>
+      </c>
+      <c r="E838" t="n">
+        <v>2671.2</v>
+      </c>
+      <c r="F838" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G838" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B839" t="n">
+        <v>20090.4</v>
+      </c>
+      <c r="C839" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D839" t="n">
+        <v>2542.6</v>
+      </c>
+      <c r="E839" t="n">
+        <v>2549.7</v>
+      </c>
+      <c r="F839" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G839" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B840" t="n">
+        <v>19779.1</v>
+      </c>
+      <c r="C840" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2331.1</v>
+      </c>
+      <c r="E840" t="n">
+        <v>2622.5</v>
+      </c>
+      <c r="F840" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G840" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B841" t="n">
+        <v>19733.4</v>
+      </c>
+      <c r="C841" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D841" t="n">
+        <v>2644.6</v>
+      </c>
+      <c r="E841" t="n">
+        <v>2682.6</v>
+      </c>
+      <c r="F841" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G841" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B842" t="n">
+        <v>19685.8</v>
+      </c>
+      <c r="C842" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2620.1</v>
+      </c>
+      <c r="E842" t="n">
+        <v>2665.6</v>
+      </c>
+      <c r="F842" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G842" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B843" t="n">
+        <v>19689</v>
+      </c>
+      <c r="C843" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D843" t="n">
+        <v>2681.1</v>
+      </c>
+      <c r="E843" t="n">
+        <v>2682.3</v>
+      </c>
+      <c r="F843" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G843" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B844" t="n">
+        <v>19924.8</v>
+      </c>
+      <c r="C844" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D844" t="n">
+        <v>2773.7</v>
+      </c>
+      <c r="E844" t="n">
+        <v>2546.4</v>
+      </c>
+      <c r="F844" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G844" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B845" t="n">
+        <v>20087.2</v>
+      </c>
+      <c r="C845" t="n">
+        <v>61172.9</v>
+      </c>
+      <c r="D845" t="n">
+        <v>2739.9</v>
+      </c>
+      <c r="E845" t="n">
+        <v>2565.5</v>
+      </c>
+      <c r="F845" t="n">
+        <v>225187.5</v>
+      </c>
+      <c r="G845" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
